--- a/dist/output.xlsx
+++ b/dist/output.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +43,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FF0000"/>
         <bgColor rgb="00FF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,14 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -513,970 +506,1096 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>06:24:36</t>
+        <v>45758</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>18:56:53</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>17:29:48</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SONIA</t>
+          <t>NICOLAY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QUILA TRUJILLO</t>
+          <t>ALEX PONCE FREYRE</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>06:57:43</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>13:00:58</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>14:01:08</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>17:02:29</t>
-        </is>
-      </c>
+        <v>45759</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>12:20:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STEPHANY</t>
+          <t>SONIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOSADA FIGUEROA</t>
+          <t>QUILA TRUJILLO</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>09:56:09</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>13:01:21</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>14:00:04</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>18:59:20</t>
-        </is>
-      </c>
+        <v>45761</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>07:27:21</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>STEPHANY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ESTEBAN ARTEAGA</t>
+          <t>LOSADA FIGUEROA</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>08:09:52</t>
+        <v>45759</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>07:56:21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12:01:30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GENNY</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NOHEMI MARTINEZ MARTINEZ</t>
+          <t>ESTEBAN ARTEAGA</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45714</v>
+        <v>45759</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>08:48:33</t>
+          <t>15:06:50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>18:43:22</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>ESTEBAN ARTEAGA</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>07:58:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>12:01:55</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>13:00:02</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>17:03:55</t>
-        </is>
-      </c>
+          <t>06:59:08</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YIRETH</t>
+          <t>GENNY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SERNA HUESAQUILLO</t>
+          <t>NOHEMI MARTINEZ MARTINEZ</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>06:57:50</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>12:04:35</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>13:04:40</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>16:01:01</t>
-        </is>
-      </c>
+        <v>45758</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>17:33:15</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PAULA</t>
+          <t>GENNY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ANDREA ORDONEZ CABRERA</t>
+          <t>NOHEMI MARTINEZ MARTINEZ</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>06:58:47</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>12:01:09</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>13:00:36</t>
-        </is>
-      </c>
+        <v>45759</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>08:39:13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16:00:46</t>
+          <t>13:00:37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JANETH</t>
+          <t>GENNY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TABORDA CANO</t>
+          <t>NOHEMI MARTINEZ MARTINEZ</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>06:56:10</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>12:00:51</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>13:00:13</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>17:01:59</t>
-        </is>
-      </c>
+          <t>07:43:30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JESSIKA</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PATRICIA RIVERA CORREA</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>06:08:16</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>12:00:56</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>13:00:06</t>
-        </is>
-      </c>
+        <v>45759</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>08:58:02</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16:20:27</t>
+          <t>13:00:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ERIKA</t>
+          <t>YIRETH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DAYANA BENAVIDES HOYOS</t>
+          <t>SERNA HUESAQUILLO</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>06:56:43</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>12:01:14</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>13:00:20</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>17:01:54</t>
-        </is>
-      </c>
+          <t>07:26:09</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>PAULA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FERNANDO OSORIO ALTAMIRANO</t>
+          <t>ANDREA ORDONEZ CABRERA</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45714</v>
+        <v>45759</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>07:57:36</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>13:02:33</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>13:59:50</t>
-        </is>
-      </c>
+          <t>07:58:29</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18:00:34</t>
+          <t>11:40:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FREDDY</t>
+          <t>PAULA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANTONIO SILVA VARGAS</t>
+          <t>ANDREA ORDONEZ CABRERA</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>06:30:10</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>12:41:40</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>13:45:30</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>16:32:02</t>
-        </is>
-      </c>
+          <t>07:28:41</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MARIA</t>
+          <t>JANETH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JOSE BECERRA BERMUDEZ</t>
+          <t>TABORDA CANO</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45714</v>
+        <v>45759</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>07:58:12</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>12:36:51</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>13:34:02</t>
-        </is>
-      </c>
+          <t>07:56:34</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17:01:17</t>
+          <t>11:01:33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>JANETH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SINISTERRA CAICEDO</t>
+          <t>TABORDA CANO</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>06:56:56</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>12:02:12</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>13:02:12</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>16:07:01</t>
-        </is>
-      </c>
+          <t>06:57:10</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MARCELA</t>
+          <t>JESSIKA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANAZCO HOYOS</t>
+          <t>PATRICIA RIVERA CORREA</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>06:55:59</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>12:01:01</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>13:00:25</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>17:01:39</t>
-        </is>
-      </c>
+          <t>07:03:20</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>ERIKA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PABLO VERA</t>
+          <t>DAYANA BENAVIDES HOYOS</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>07:53:34</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>13:06:44</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>14:05:23</t>
-        </is>
-      </c>
+        <v>45759</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>08:55:14</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17:07:41</t>
+          <t>12:03:24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SOLANGIE</t>
+          <t>ERIKA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PINCHAO RODRIGUEZ</t>
+          <t>DAYANA BENAVIDES HOYOS</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>06:48:06</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>13:06:12</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>14:07:45</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>17:11:14</t>
-        </is>
-      </c>
+          <t>06:57:21</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ESTEBAN</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TABARES</t>
+          <t>FERNANDO OSORIO ALTAMIRANO</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>07:57:55</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>12:34:58</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>13:34:21</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>17:01:04</t>
-        </is>
-      </c>
+        <v>45758</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>18:00:58</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KATHERINE</t>
+          <t>FREDDY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CARDONA CAICEDO</t>
+          <t>ANTONIO SILVA VARGAS</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>09:56:14</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>13:36:23</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>14:31:17</t>
-        </is>
-      </c>
+        <v>45759</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>07:23:13</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18:59:52</t>
+          <t>10:42:29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>FREDDY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SEBASTIAN RINCONSANCHEZ</t>
+          <t>ANTONIO SILVA VARGAS</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07:57:46</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>12:31:56</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>13:31:15</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>17:03:10</t>
-        </is>
-      </c>
+          <t>06:18:24</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JEZI</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KARIME ZUNIGA ORDONEZ</t>
+          <t>SINISTERRA CAICEDO</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>06:56:49</t>
+        <v>45758</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>17:34:28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>13:07:24</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEIVI</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PATRICIA IBARRA SIMALES</t>
+          <t>SINISTERRA CAICEDO</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>07:58:27</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>13:02:38</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>13:59:54</t>
-        </is>
-      </c>
+        <v>45759</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>08:56:32</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18:00:53</t>
+          <t>13:02:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HELEN</t>
+          <t>MARCELA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIA VASQUEZ ANACONA</t>
+          <t>ANAZCO HOYOS</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>08:28:23</t>
+        <v>45759</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>07:57:30</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>15:01:30</t>
+          <t>11:01:10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ANGIE</t>
+          <t>MARCELA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARLYN RODRIGUEZ DIAZ</t>
+          <t>ANAZCO HOYOS</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45714</v>
+        <v>45761</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>07:58:20</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>12:31:45</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>13:30:05</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>17:01:45</t>
-        </is>
-      </c>
+          <t>06:57:14</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ADOLFO PRECIADO CORTES</t>
+          <t>PABLO VERA</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>45714</v>
+        <v>45759</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>06:57:36</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>12:57:41</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>13:58:15</t>
-        </is>
-      </c>
+          <t>08:00:24</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>16:02:06</t>
+          <t>12:02:29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>95</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PABLO VERA</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:58:47</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>96</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SOLANGIE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PINCHAO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>06:58:27</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>99</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ESTEBAN</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TABARES</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>08:58:17</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>13:00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>100</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>KATHERINE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CARDONA CAICEDO</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>07:56:03</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>12:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>102</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEBASTIAN RINCONSANCHEZ</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>07:58:54</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>12:02:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>102</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEBASTIAN RINCONSANCHEZ</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>07:27:38</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>104</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JEZI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>KARIME ZUNIGA ORDONEZ</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>08:58:28</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>12:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>105</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DEIVI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PATRICIA IBARRA SIMALES</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>45758</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>18:06:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>105</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DEIVI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PATRICIA IBARRA SIMALES</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>08:58:38</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>12:01:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>106</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HELEN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MARIA VASQUEZ ANACONA</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>07:56:45</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>11:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>109</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>JUAN</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>BAHOS LUGO</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>07:58:42</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="D38" s="2" t="n">
+        <v>45758</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>18:13:32</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>109</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BAHOS LUGO</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:59:48</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>110</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BRIHAN</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BOLANOS GALLO</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>45758</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>18:01:12</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>110</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BRIHAN</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BOLANOS GALLO</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>08:58:34</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
         <is>
           <t>12:01:23</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>13:00:30</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>17:03:05</t>
         </is>
       </c>
     </row>
